--- a/pacjenci/SEBASTIAN TAMASIK.xlsx
+++ b/pacjenci/SEBASTIAN TAMASIK.xlsx
@@ -586,17 +586,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4 - wychwyt umiarkowanie większy od wątroby</t>
+          <t>4 - utrzymujący się wychwyt patologiczny</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Częściowa odpowiedź metaboliczna na leczenie. Klasyfikacja Lugano: Partial Response (PR) - częściowa odpowiedź na leczenie. Deauville: 4 - wychwyt umiarkowanie większy od wątroby.</t>
+          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brak aktywnej choroby</t>
+          <t>Do oceny</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -630,17 +630,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3 - wychwyt nie większy niż wątroba</t>
+          <t>4 - utrzymujący się wychwyt patologiczny</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Nie stwierdza się aktywnej metabolicznie choroby. Klasyfikacja Lugano: Complete Response (CR) - całkowita odpowiedź na leczenie. Deauville: 3 - wychwyt nie większy niż wątroba.</t>
+          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
         </is>
       </c>
     </row>

--- a/pacjenci/SEBASTIAN TAMASIK.xlsx
+++ b/pacjenci/SEBASTIAN TAMASIK.xlsx
@@ -413,235 +413,176 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Nr badania</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Data badania</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Nr badania</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Etap leczenia</t>
+          <t>Problem kliniczny</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Linia leczenia</t>
+          <t>Zakres badania</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Rozpoznanie</t>
+          <t>Opis badania</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Opis</t>
+          <t>Wnioski</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
           <t>SUVmax</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Ocena odpowiedzi</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Deauville</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Wnioski</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>28.09.2020</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina. Ocena zaawansowania klinicznego.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po  61min od podania 18F-FDG. Glikemia: 87mg%</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Asymetryczna aktywność metaboliczna w topografii ślinianki podżuchwowej lewej, SUV max 3,8 - czynnościowa? do oceny klinicznej. Aktywne i pobudzone metabolicznie węzły chłonne grupy: - 1B po stronie lewej średnicy wg PET 10mm, SUV max 3,7 [lm fuz 64], - 2 po stronie prawej średnicy wg PET do 24mm, SUV max do 10,1, - nadobojczykowe lewe średnicy do 9mm, SUV max do 2,4. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi.  Klatka piersiowa i śródpiersie: Aktywne metabolicznie węzły chłonne: -  okna aortalno-płucnego średnicy wg PET do 10mm, SUV max 3,8, -  położone lewobocznie od łuku aorty średnicy wg PET 11mm, SUV max 3,9, -  podostrogowe wielkości wg PET do 10mm, SUV max do 3,8, -  wnęki płuca lewego średnicy wg PET 12mm, SUV max do 4,3, -  przyosierdziowy po stronie prawej średnicy wg PET 13mm, SUV max 5,8. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia.  Brzuch i miednica: W obu płatach wątroby  liczne aktywne metabolicznie obszary średnicy wg PET do 18mm, SUV max do 6,7. Niejednorodny metabolizm FDG w śledzionie, SUV max do 3,6. Liczne aktywne metabolicznie węzły chłonne: - okolicy krzywizny mniejszej żołądka, wnęki wątroby oraz okolicy głowy trzustki wielkości wg PET do 47x31mm, SUV max do 7,4, - okołoaortalne obustronnie na wysokości nerek wielkości wg PET po stronie lewej do 22x43mm, po stronie prawej do 18x32SUV max do 10,8, - krezkowe średnicy wg PET do 16mm, SUV max do7,2. Pobudzenie metaboliczne w prawym płacie prostaty - SUV max 5,9  - do konsultacji urologicznej. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Torbiel nerki lewej średnicy 14mm.  Układ kostny: Liczne aktywne metabolicznie obszary w obrębie czaszki, mostka, łopatek, żeber, kręgosłupa, kości miednicy, kości ramiennych i udowych, wielkości wg PET do 35x20mm, SUV max do 17,6 (w trzonie kości biodrowej prawej).  Wartości referencyjne: MBPS SUVmax 1,8, Prawy płat wątroby SUVmax do 3,5.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono aktywną metabolicznie chorobę chłoniakową z zajęciem węzłów chłonnych po obu stronach przepony,  wątroby oraz kości. Niewykluczone zajęcie śledziony oraz prostaty.</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>17.6</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Nie dotyczy</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Aktywna metabolicznie choroba przed rozpoczęciem leczenia. Badanie wyjściowe stanowiące punkt odniesienia.</t>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>03.12.2020</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina. Wczesna ocena odpowiedzi.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po  57min od podania 18F-FDG. Glikemia: 92mg%.</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Wydatne zwapnienia w przedniej części sierpu mózgu.  Klatka piersiowa i śródpiersie: Aktywne metabolicznie bardzo liczne zmiany drobnoguzkowe i naciekowe w miąższu płuca prawego, najbardziej nasilone w płacie górnym i środkowym, wielkości od 3mm do 25x22 mm wg PET, SUV max do 6,0. Wzmożony metabolizm FDG w węzłach chłonnych: - przytchawiczych dolnych prawych wielkości do 10 mm SUV max do 2,7; - wnęki płuca prawego wielkości do 13 mm SUV max do 3,3;  Wzmożony metabolizm FDG w dolnej części przełyku SUV max do 5,1 - w pierwszej kolejności o charakterze odczynowym. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Drobne węzły chłonne oraz masa miękkotkankowa w nadbrzuszu po stronie prawej, pomiędzy trzustką a płatem ogoniastym wątroby, wielkości ok. 36x21 mm SUV max do 2,7 [Im CT 454] Niejednorodny metabolizm FDG w prostacie  - do konsultacji urologicznej. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Torbiel korowa nerki lewej średnicy 14mm. Dość liczne węzły chłonne okołoaortalne po stronie lewej na wysokości nerek wielkości  do 20x15 mm.  Układ kostny: Rozlanie wzmożony metabolizm FDG w układzie kostnym objętym badaniem. Nieznaczna esowata skolioza kręgosłupa: prawowypukła w odcinku piersiowym i lewowypukła w odcinku lędźwiowym kręgosłupa. Pojedyncze drobne guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Lumbalizacja kręgu S1, z zachowaną wąską przestrzenią międzykręgową na poziomie S1/S2. Os sacrum arcuatum.  Wartości referencyjne: MBPS SUVmax 1,8; Prawy płat wątroby SUVmax do 3,0.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnych metabolicznie bardzo licznych zmian drobnoguzkowych i naciekowych w miąższu płuca prawego- zmiany w przebiegu choroby zasadniczej? zmiany zapalne?- do interpretacji z całością obrazu klinicznego. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>6</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>22.04.2021</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina. Ocena odpowiedzi po II cyklach BGD.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 62min od podania 18F-FDG. Glikemia: 90mg%.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Wydatne zwapnienia w przedniej części sierpu mózgu.  Klatka piersiowa i śródpiersie: Drobny aktywny metabolicznie obszar  podopłucnowo w segmencie 4 płuca prawego  na obszarze wielkości ok 31x16mm wg PET, SUV max do 3,6. Pobudzenie metaboliczne w bliźnie w okolicy dołu pachowego prawego  SUV max 1,9 Wzmożony metabolizm FDG w dolnej części przełyku SUV max do 3,8 - w pierwszej kolejności o charakterze odczynowym. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Niejednorodny metabolizm FDG w prostacie, ogniskowo zwiększony po stronie prawej, SUV max do 5,1 - do konsultacji urologicznej. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Torbiel korowa nerki lewej średnicy 14mm. Dość liczne węzły chłonne okołoaortalne po stronie lewej na wysokości nerek wielkości  do 20x15 mm.  Układ kostny: Rozlanie wzmożony metabolizm FDG w układzie kostnym objętym badaniem. Nieznaczna esowata skolioza kręgosłupa: prawowypukła w odcinku piersiowym i lewowypukła w odcinku lędźwiowym kręgosłupa. Pojedyncze drobne guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Lumbalizacja kręgu S1, z zachowaną wąską przestrzenią międzykręgową na poziomie S1/S2. Os sacrum arcuatum.  Wartości referencyjne: MBPS SUVmax 2,1; Prawy płat wątroby SUVmax do 2,7.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność pojedynczego aktywnego metabolicznie obszaru  w segmencie 4 płuca prawego - zmiany w przebiegu choroby zasadniczej? zmiany zapalne? - do interpretacji z całością obrazu klinicznego. Poza tym uwidoczniono regresję metaboliczną pozostałych opisywanych zmian.</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>5.1</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>14.06.2021</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>4</v>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina. Ocena remisji choroby.</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 56min od podania 18F-FDG. Glikemia: 100mg%.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Asymetrycznie wzmożony metabolizm FDG w powiększonej śliniance podżuchwowej lewej SUV max do 3,7 - wskazana kontrola w USG. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Wydatne zwapnienia w przedniej części sierpu mózgu.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Zwiększona densyjność tkanki tłuszczowej w śródpiersiu przednim. Szwy metalowe w miąższu płuca prawego Niewielkie zmiany włókniste w segmentach 5 obu płuc i obustronnie nadprzeponowo.  Brzuch i miednica: Rozlanie wzmożony metabolizm FDG w żołądku SUV max do 5,1- odczynowo? Rozlanie i odcinkowo wzmożony metabolizm FDG w jelitach SUV max do 5,6- czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Aktualnie słabo wyodrębniająca się torbiel korowa nerki lewej średnicy 14mm- do kontroli w USG.  Węzły chłonne okołoaortalne po stronie lewej na wysokości nerek, wielkości  do 16x13mm. Węzły chłonne pachwinowe obustronnie wielkości do 12x9mm.  Układ kostny: Niejednorodny metabolizm FDG w układzie kostnym objętym badaniem. Nieznaczna esowata skolioza kręgosłupa: prawowypukła w odcinku piersiowym i lewowypukła w odcinku lędźwiowym kręgosłupa. Pojedyncze drobne guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Lumbalizacja kręgu S1, z zachowaną wąską przestrzenią międzykręgową na poziomie S1/S2. Os sacrum arcuatum.  Inne: Miernie pobudzone metabolicznie zagęszczenia w tkance podskórnej okolicy lędźwiowej prawej oraz w tkance podskórnej obu pośladków SUV max do 2,3 - w pierwszej kolejności zmiany poiniekcyjne.  Wartości referencyjne: MBPS SUVmax 1,8; Prawy płat wątroby SUVmax do 3,4.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono obecności aktywnej metabolicznie choroby chłoniakowej. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>5.6</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
       </c>
     </row>
   </sheetData>
